--- a/data/trans_orig/KC10IN_T-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/KC10IN_T-Habitat-trans_orig.xlsx
@@ -489,7 +489,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>KIDSCREEN autopercibido (escala)</t>
+          <t>KIDSCREEN autopercibido (escala) (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -571,17 +571,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>55,2; 59,36</t>
+          <t>55,09; 59,39</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>55,84; 74,83</t>
+          <t>55,87; 74,04</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>56,12; 69,83</t>
+          <t>56,14; 69,89</t>
         </is>
       </c>
     </row>
@@ -621,17 +621,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>55,13; 59,67</t>
+          <t>55,15; 59,56</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>53,68; 57,79</t>
+          <t>53,56; 57,79</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>54,69; 57,64</t>
+          <t>54,58; 57,72</t>
         </is>
       </c>
     </row>
@@ -671,17 +671,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>53,89; 63,74</t>
+          <t>53,42; 63,33</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>59,96; 68,3</t>
+          <t>59,94; 68,59</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>56,54; 64,6</t>
+          <t>56,27; 64,49</t>
         </is>
       </c>
     </row>
@@ -721,17 +721,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>54,47; 58,49</t>
+          <t>54,34; 58,28</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>54,74; 60,13</t>
+          <t>54,75; 59,99</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>55,28; 58,44</t>
+          <t>55,2; 58,4</t>
         </is>
       </c>
     </row>
@@ -771,17 +771,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>55,24; 58,75</t>
+          <t>55,03; 58,74</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>57,44; 63,15</t>
+          <t>57,44; 62,69</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>56,9; 60,29</t>
+          <t>57,0; 60,47</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/KC10IN_T-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/KC10IN_T-Habitat-trans_orig.xlsx
@@ -571,17 +571,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>55,09; 59,39</t>
+          <t>55,24; 59,49</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>55,87; 74,04</t>
+          <t>55,41; 73,44</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>56,14; 69,89</t>
+          <t>56,1; 69,68</t>
         </is>
       </c>
     </row>
@@ -621,17 +621,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>55,15; 59,56</t>
+          <t>55,22; 59,41</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>53,56; 57,79</t>
+          <t>53,74; 57,7</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>54,58; 57,72</t>
+          <t>54,57; 57,63</t>
         </is>
       </c>
     </row>
@@ -671,17 +671,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>53,42; 63,33</t>
+          <t>53,59; 63,86</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>59,94; 68,59</t>
+          <t>59,74; 68,27</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>56,27; 64,49</t>
+          <t>56,71; 64,34</t>
         </is>
       </c>
     </row>
@@ -721,17 +721,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>54,34; 58,28</t>
+          <t>54,29; 58,4</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>54,75; 59,99</t>
+          <t>54,84; 59,97</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>55,2; 58,4</t>
+          <t>55,04; 58,36</t>
         </is>
       </c>
     </row>
@@ -771,17 +771,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>55,03; 58,74</t>
+          <t>55,01; 58,64</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>57,44; 62,69</t>
+          <t>57,3; 62,15</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>57,0; 60,47</t>
+          <t>57,09; 60,49</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/KC10IN_T-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/KC10IN_T-Habitat-trans_orig.xlsx
@@ -495,12 +495,12 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t>Niña</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -548,17 +548,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>57,04</t>
+          <t>61,5</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>62,9</t>
+          <t>56,82</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>60,57</t>
+          <t>59,53</t>
         </is>
       </c>
     </row>
@@ -571,17 +571,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>55,24; 59,49</t>
+          <t>55,66; 73,06</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>55,41; 73,44</t>
+          <t>55,06; 59,12</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>56,1; 69,68</t>
+          <t>55,93; 67,55</t>
         </is>
       </c>
     </row>
@@ -598,17 +598,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>57,08</t>
+          <t>55,84</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>55,78</t>
+          <t>56,96</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>56,23</t>
+          <t>56,24</t>
         </is>
       </c>
     </row>
@@ -621,17 +621,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>55,22; 59,41</t>
+          <t>53,91; 57,86</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>53,74; 57,7</t>
+          <t>55,0; 59,5</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>54,57; 57,63</t>
+          <t>54,85; 57,65</t>
         </is>
       </c>
     </row>
@@ -648,17 +648,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>58,33</t>
+          <t>63,39</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>63,74</t>
+          <t>62,04</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>60,91</t>
+          <t>62,81</t>
         </is>
       </c>
     </row>
@@ -671,17 +671,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>53,59; 63,86</t>
+          <t>59,63; 67,84</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>59,74; 68,27</t>
+          <t>58,91; 65,33</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>56,71; 64,34</t>
+          <t>60,5; 65,64</t>
         </is>
       </c>
     </row>
@@ -698,17 +698,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>56,2</t>
+          <t>57,1</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>57,16</t>
+          <t>56,09</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>56,68</t>
+          <t>56,58</t>
         </is>
       </c>
     </row>
@@ -721,17 +721,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>54,29; 58,4</t>
+          <t>54,76; 60,06</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>54,84; 59,97</t>
+          <t>54,37; 58,37</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>55,04; 58,36</t>
+          <t>55,2; 58,39</t>
         </is>
       </c>
     </row>
@@ -748,17 +748,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>57,28</t>
+          <t>58,93</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>59,24</t>
+          <t>57,94</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>58,38</t>
+          <t>58,51</t>
         </is>
       </c>
     </row>
@@ -771,17 +771,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>55,01; 58,64</t>
+          <t>57,29; 62,02</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>57,3; 62,15</t>
+          <t>56,75; 59,14</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>57,09; 60,49</t>
+          <t>57,36; 60,14</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/KC10IN_T-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/KC10IN_T-Habitat-trans_orig.xlsx
@@ -16,7 +16,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.##"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -97,7 +99,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -110,6 +112,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -476,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E14"/>
+  <dimension ref="A1:E19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -489,7 +494,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>KIDSCREEN autopercibido (escala) (tasa de respuesta: 100,0%)</t>
+          <t>KIDSCREEN autopercibido (escala) (tasa de respuesta: 29,74%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -546,149 +551,109 @@
           <t>Media</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>61,5</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>56,82</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>59,53</t>
-        </is>
+      <c r="C4" s="5" t="n">
+        <v>61.5038148515839</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>56.8159484779259</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>59.52841700065896</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>55,66; 73,06</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>55,06; 59,12</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>55,93; 67,55</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>55.6597928595524</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>55.05669738943863</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>55.93025068883798</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="inlineStr">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>73.06246509908384</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>59.12142624967485</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>67.54769842847674</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
         <is>
           <t>10-50.000 hab</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>Media</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>55,84</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>56,96</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>56,24</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n"/>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>53,91; 57,86</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>55,0; 59,5</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>54,85; 57,65</t>
-        </is>
+      <c r="C7" s="5" t="n">
+        <v>55.84198482936408</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>56.95611622978658</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>56.24129354846943</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>&gt;50.000 hab</t>
-        </is>
-      </c>
+      <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Media</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>63,39</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>62,04</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>62,81</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>53.91400107452828</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>55.00238552837948</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>54.8462740893337</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>59,63; 67,84</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>58,91; 65,33</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>60,5; 65,64</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>57.86062119610343</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>59.50184114353602</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>57.65489856408248</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>Capitales</t>
+          <t>&gt;50.000 hab</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -696,97 +661,162 @@
           <t>Media</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>57,1</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>56,09</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>56,58</t>
-        </is>
+      <c r="C10" s="5" t="n">
+        <v>63.38790053627793</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>62.03691911307838</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>62.8100714348045</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>54,76; 60,06</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>54,37; 58,37</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>55,2; 58,39</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>59.63000070173838</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>58.91007459842427</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>60.50174633535401</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="inlineStr">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>67.83552444616879</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>65.32530925089542</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>65.63909491336328</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Capitales</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>57.10291732838874</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>56.08616713298438</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>56.58217722714993</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>54.75658124503642</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>54.36616715299995</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>55.20042756984557</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>60.06149693490292</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>58.37189458491219</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>58.3870990638079</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="B12" s="3" t="inlineStr">
+      <c r="B16" s="3" t="inlineStr">
         <is>
           <t>Media</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>58,93</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>57,94</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>58,51</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="n"/>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>57,29; 62,02</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>56,75; 59,14</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>57,36; 60,14</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
+      <c r="C16" s="5" t="n">
+        <v>58.92573356494936</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>57.93558560135788</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>58.50662137489838</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="n">
+        <v>57.28806576354001</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>56.74706226701043</v>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>57.3591037734431</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="n">
+        <v>62.02226257352562</v>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>59.1375121271623</v>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>60.13804743013878</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
         </is>
@@ -794,12 +824,12 @@
     </row>
   </sheetData>
   <mergeCells count="6">
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="A4:A5"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
     <mergeCell ref="A1:B2"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="A13:A15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
